--- a/data/trans_orig/IP17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27274</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>51607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63593</t>
+          <t>63581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76564</t>
+          <t>76641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59392</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72030</t>
+          <t>72263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127958</t>
+          <t>126105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145427</t>
+          <t>145477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67554</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92964</t>
+          <t>92706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91636</t>
+          <t>91616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121591</t>
+          <t>120915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166910</t>
+          <t>167129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205969</t>
+          <t>207509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>323123</t>
+          <t>323381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348533</t>
+          <t>348098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355400</t>
+          <t>356076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>385355</t>
+          <t>385375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687109</t>
+          <t>685569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726168</t>
+          <t>725949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>43850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58358</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81201</t>
+          <t>82024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>131172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146780</t>
+          <t>147969</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112974</t>
+          <t>114288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130230</t>
+          <t>131213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251004</t>
+          <t>250181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273847</t>
+          <t>274263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116961</t>
+          <t>116903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149439</t>
+          <t>151293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143641</t>
+          <t>143154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181542</t>
+          <t>180250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271698</t>
+          <t>272887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>317884</t>
+          <t>321100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531582</t>
+          <t>529728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>564060</t>
+          <t>564118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540432</t>
+          <t>541724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578333</t>
+          <t>578820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1085111</t>
+          <t>1081895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1131297</t>
+          <t>1130108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26469</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,49 +2351,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17351</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12406</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24702</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>14,39%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>28,66%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17351</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11809</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24719</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>28,68%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>55</t>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28068</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46111</t>
+          <t>46537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65900</t>
+          <t>65549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78797</t>
+          <t>78251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,47 +2464,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>68841</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>61490</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73786</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>71,34%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68841</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61473</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74383</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,87%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>71,32%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132450</t>
+          <t>132024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150493</t>
+          <t>149510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86705</t>
+          <t>87103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115291</t>
+          <t>116094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107609</t>
+          <t>107633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139976</t>
+          <t>138965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197777</t>
+          <t>203081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241768</t>
+          <t>243745</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336156</t>
+          <t>335353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364742</t>
+          <t>364344</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352171</t>
+          <t>353182</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>384538</t>
+          <t>384514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701826</t>
+          <t>699849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745817</t>
+          <t>740513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>34887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55158</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39988</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63265</t>
+          <t>62895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88496</t>
+          <t>88835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110980</t>
+          <t>112730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130826</t>
+          <t>131251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132240</t>
+          <t>131933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148501</t>
+          <t>148945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249870</t>
+          <t>249531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275101</t>
+          <t>275471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>145285</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180809</t>
+          <t>183629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152584</t>
+          <t>151019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191075</t>
+          <t>189517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308072</t>
+          <t>306933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>360647</t>
+          <t>362347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>529144</t>
+          <t>526324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>564433</t>
+          <t>564668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>559492</t>
+          <t>561050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>597983</t>
+          <t>599548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1099874</t>
+          <t>1098174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1152449</t>
+          <t>1153588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25348</t>
+          <t>25495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39594</t>
+          <t>39498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34030</t>
+          <t>33883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45707</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>61088</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88399</t>
+          <t>88495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104205</t>
+          <t>104215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80285</t>
+          <t>79656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108377</t>
+          <t>107140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82503</t>
+          <t>82171</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112383</t>
+          <t>111044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169105</t>
+          <t>167209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209281</t>
+          <t>208567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363217</t>
+          <t>364454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391309</t>
+          <t>391938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373728</t>
+          <t>375067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403608</t>
+          <t>403940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>749138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>788600</t>
+          <t>790496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40454</t>
+          <t>41382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28767</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>47045</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56443</t>
+          <t>57698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80894</t>
+          <t>81782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131643</t>
+          <t>130715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148070</t>
+          <t>147675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139586</t>
+          <t>139087</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157675</t>
+          <t>157365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277335</t>
+          <t>276447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301786</t>
+          <t>300531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128350</t>
+          <t>127645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163278</t>
+          <t>161928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>129843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164987</t>
+          <t>164378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264740</t>
+          <t>266751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>313988</t>
+          <t>316631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539792</t>
+          <t>541142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574720</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575870</t>
+          <t>576479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611451</t>
+          <t>611014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1129939</t>
+          <t>1127296</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1179187</t>
+          <t>1177176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23380</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>43284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51601</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>45994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>56701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93302</t>
+          <t>93053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106304</t>
+          <t>105875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52550</t>
+          <t>50885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81761</t>
+          <t>81530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74791</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108118</t>
+          <t>109264</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135641</t>
+          <t>137760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180381</t>
+          <t>180786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377933</t>
+          <t>378164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407144</t>
+          <t>408809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>408501</t>
+          <t>407355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441828</t>
+          <t>439233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>795932</t>
+          <t>795527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>840672</t>
+          <t>838553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22479</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47986</t>
+          <t>46915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72950</t>
+          <t>70132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112542</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129435</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141674</t>
+          <t>142099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160870</t>
+          <t>161621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259950</t>
+          <t>262768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284914</t>
+          <t>285985</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83813</t>
+          <t>83018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121108</t>
+          <t>116624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113277</t>
+          <t>113296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>151520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206243</t>
+          <t>208300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260478</t>
+          <t>257858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>542815</t>
+          <t>547299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>580110</t>
+          <t>580905</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>612244</t>
+          <t>610452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648695</t>
+          <t>648676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1165417</t>
+          <t>1168037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1219652</t>
+          <t>1217595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20622</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14583</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27368</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19978</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14226</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27286</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14138</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26784</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20622</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14582</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27672</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,75%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32235</t>
+          <t>31972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51607</t>
+          <t>50661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66223</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59477</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72262</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63581</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>76641</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64083</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76729</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66223</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59173</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72263</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,25%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126105</t>
+          <t>127051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>145740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>105969</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>92144</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>120769</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>79372</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>67989</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>92706</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>66230</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>91866</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>105969</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>91616</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>120915</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167129</t>
+          <t>165174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207509</t>
+          <t>204278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>371022</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>356222</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>384847</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>336715</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>323381</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>348098</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>324221</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>349857</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>371022</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>356076</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>385375</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>77,78%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685569</t>
+          <t>688800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725949</t>
+          <t>727904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35246</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26622</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43376</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>34237</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26097</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42894</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26030</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42821</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35246</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>26925</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>43850</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57942</t>
+          <t>57997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82024</t>
+          <t>81722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>122892</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114762</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131516</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>139829</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>131172</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147969</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>131245</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148036</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>122892</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>114288</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131213</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250181</t>
+          <t>250483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274263</t>
+          <t>274208</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>144815</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>181338</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>133587</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>116903</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>151293</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>118374</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>150599</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>161836</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>143154</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>180250</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>272887</t>
+          <t>271796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321100</t>
+          <t>320791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>560138</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>540636</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>577159</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>817</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>547434</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>529728</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>564118</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>530422</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>562647</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>843</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>560138</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>541724</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>578820</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1081895</t>
+          <t>1082204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1130108</t>
+          <t>1131199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2012 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17351</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12080</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24464</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19379</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14118</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26820</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13544</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26322</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17351</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12406</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24702</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29051</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46537</t>
+          <t>46449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68841</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61728</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74112</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>72990</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65549</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78251</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>66047</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>78825</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>79,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68841</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61490</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73786</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>132112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149510</t>
+          <t>150163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,1%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>122092</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>108189</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>138572</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>99983</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>87103</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>116094</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>86724</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>115062</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>122092</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>107633</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>138965</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>203081</t>
+          <t>200941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243745</t>
+          <t>244941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>370055</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>353575</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>383958</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>351464</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>335353</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>364344</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>336385</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>364723</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>370055</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>353182</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>384514</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699849</t>
+          <t>698653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740513</t>
+          <t>742653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>451447</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>451447</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>451447</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31137</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23557</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40283</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>43783</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34887</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53408</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34958</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54055</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31137</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>23283</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>40295</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62895</t>
+          <t>63618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88835</t>
+          <t>88738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141091</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131945</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148671</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122355</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>112730</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>131251</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>112083</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>131180</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>73,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141091</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131933</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148945</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249531</t>
+          <t>249628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275471</t>
+          <t>274748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166138</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166138</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166138</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>151568</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>189843</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>163145</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>145285</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>183629</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>143342</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>180478</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>151019</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>189517</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>306933</t>
+          <t>307930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362347</t>
+          <t>358551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>579986</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>560724</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>598999</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>546808</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>526324</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>564668</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>529475</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>566611</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>77,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>579986</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>561050</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>599548</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,27%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1098174</t>
+          <t>1101970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1153588</t>
+          <t>1152591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>750567</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>750567</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>750567</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>709953</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>709953</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>709953</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>750567</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>750567</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>750567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2016 (tasa de respuesta: 99,62%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12114</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7805</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19010</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19229</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13858</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25495</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14066</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25805</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12114</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7526</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18192</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49604</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60809</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>40149</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33883</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45520</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33573</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45312</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,62%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56500</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50422</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61088</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88495</t>
+          <t>88335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104215</t>
+          <t>104404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>96669</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82064</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>111001</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>92829</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>79656</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>107140</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>79663</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>106072</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,68%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>16,89%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>96669</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>82171</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>111044</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167209</t>
+          <t>170128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>210595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -4385,74 +4385,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>389442</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>375110</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>404047</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>567</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>378765</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>364454</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>391938</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>365522</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>391931</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>77,51%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>83,11%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>389442</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>375067</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>403940</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>77,16%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>83,1%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1116</t>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>749138</t>
+          <t>747110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>790496</t>
+          <t>787577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>471594</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>471594</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>471594</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37335</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29543</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47145</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>31829</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24422</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41382</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24016</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>40302</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37335</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>28767</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>47045</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81782</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148797</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138987</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156589</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,13%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>140268</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130715</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147675</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>131795</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148081</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148797</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>139087</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>157365</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,94%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276447</t>
+          <t>276215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>300531</t>
+          <t>301165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186132</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186132</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186132</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172097</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172097</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172097</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186132</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186132</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>127328</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>163833</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>143886</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>127645</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>161928</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>126750</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>161597</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>146119</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>129843</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>164378</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266751</t>
+          <t>266309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316631</t>
+          <t>314781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>594738</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>577024</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>613529</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>836</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>559184</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>541142</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>575425</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>541473</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>576320</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>594738</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>576479</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>611014</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1127296</t>
+          <t>1129146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1177176</t>
+          <t>1177618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -5189,52 +5189,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>740857</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>703070</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>703070</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>703070</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>740857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han necesitado consulta con el médico por algún problema/molestia/enfermedad en las últimas 2 semanas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han necesitado consulta médica por algún problema/molestia/enfermedad en las últimas 2 semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5454</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15082</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11394</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47641</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41650</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51278</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48133</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43284</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51383</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>40804</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45994</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56701</t>
+          <t>43442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>100703</t>
+          <t>88445</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93053</t>
+          <t>81566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105875</t>
+          <t>92994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>69047</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>99850</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>66237</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>50885</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>81530</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77386</t>
+          <t>50179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109264</t>
+          <t>75294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147032</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137760</t>
+          <t>127146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180786</t>
+          <t>167023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>391871</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>375828</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>406631</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>544</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>393457</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>378164</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>408809</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>425370</t>
+          <t>368376</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>407355</t>
+          <t>356308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439233</t>
+          <t>381423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>818826</t>
+          <t>760248</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>795527</t>
+          <t>740257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>838553</t>
+          <t>780134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20343</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37720</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20774</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35898</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>34596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>44055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70132</t>
+          <t>67928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>139595</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130699</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>122020</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113653</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>128777</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>81,59%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152439</t>
+          <t>123644</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142099</t>
+          <t>115380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161621</t>
+          <t>130449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>274459</t>
+          <t>263240</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>262768</t>
+          <t>250467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285985</t>
+          <t>274340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105312</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>138293</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>83018</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>116624</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113296</t>
+          <t>80789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151520</t>
+          <t>110508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217233</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>208300</t>
+          <t>194488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257858</t>
+          <t>239724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>579107</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>562536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>595517</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>788</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>563609</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>547299</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>580905</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>630380</t>
+          <t>532824</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>610452</t>
+          <t>517828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648676</t>
+          <t>547547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1193989</t>
+          <t>1111932</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1168037</t>
+          <t>1089441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1217595</t>
+          <t>1134677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
